--- a/dati.xlsx
+++ b/dati.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3786" uniqueCount="1355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3846" uniqueCount="1374">
   <si>
     <t>Codice</t>
   </si>
@@ -347,7 +347,7 @@
     <t>BAR3978</t>
   </si>
   <si>
-    <t>BARTOLINI 25</t>
+    <t>BARTOLINI 25 (PERSA 25 26)</t>
   </si>
   <si>
     <t>Via Bartolini Lorenzo, 25</t>
@@ -1301,7 +1301,7 @@
     <t>fra3448</t>
   </si>
   <si>
-    <t>FRAPOLLI, 3</t>
+    <t>FRAPOLLI, 3( PERSA 25-26)</t>
   </si>
   <si>
     <t>Via Frapolli, 3</t>
@@ -2228,7 +2228,7 @@
     <t>Par4288</t>
   </si>
   <si>
-    <t>Partigiani d'Italia 24</t>
+    <t>PARTIGIANI D'ITALIA 24 CONDOMINIO P3</t>
   </si>
   <si>
     <t>Via Partigiani d'Italia, 24</t>
@@ -2291,7 +2291,7 @@
     <t>PEL4600</t>
   </si>
   <si>
-    <t>PELLEGRINO ROSSI 44</t>
+    <t>PELLEGRINO ROSSI 44( PERSA 25-26)</t>
   </si>
   <si>
     <t>Via Rossi Pellegrino, 44</t>
@@ -2969,7 +2969,7 @@
     <t>VIA6231</t>
   </si>
   <si>
-    <t>VENINI 58</t>
+    <t>VENINI 58 ( PERSA 25-26)</t>
   </si>
   <si>
     <t>Via Venini Giulio E Corrado, 58</t>
@@ -2981,7 +2981,7 @@
     <t>Ver5738</t>
   </si>
   <si>
-    <t>Verdi 6-8-10</t>
+    <t>VERDI 6-8-10 ( PERSA 25-26)</t>
   </si>
   <si>
     <t>Via Verdi Giuseppe, 6/8</t>
@@ -3155,7 +3155,7 @@
     <t>MONTE SAN MICHELE 108</t>
   </si>
   <si>
-    <t>Via Monte san Michele, 108</t>
+    <t>Via monte san michele 108, 108</t>
   </si>
   <si>
     <t>94538950158</t>
@@ -3449,7 +3449,7 @@
     <t>RAV8870</t>
   </si>
   <si>
-    <t>RAVIZZA 36( PERSA 25-26)</t>
+    <t>RAVIZZA 36</t>
   </si>
   <si>
     <t>Via Ravizza Carlo, 36</t>
@@ -3686,7 +3686,7 @@
     <t>MAG3819</t>
   </si>
   <si>
-    <t>I MAGGIO 23</t>
+    <t>I MAGGIO 23 RHO</t>
   </si>
   <si>
     <t>Via I MAGGIO, 23</t>
@@ -3761,7 +3761,7 @@
     <t>CAV8566</t>
   </si>
   <si>
-    <t>CAVOUR 62/A CORSICO</t>
+    <t>CAVOUR 62/A CORSICO( PERSA 25-26)</t>
   </si>
   <si>
     <t>Via Cavour, 62</t>
@@ -3836,7 +3836,7 @@
     <t>FOR1081</t>
   </si>
   <si>
-    <t>FORZE ARMATE 360</t>
+    <t>FORZE ARMATE 360 PERSA</t>
   </si>
   <si>
     <t>Via delle Forze Armate, 360</t>
@@ -3980,6 +3980,18 @@
     <t>Via Palmieri Nicola, 72</t>
   </si>
   <si>
+    <t>COR5744</t>
+  </si>
+  <si>
+    <t>CORREGGIO 8</t>
+  </si>
+  <si>
+    <t>Via correggio, 8</t>
+  </si>
+  <si>
+    <t>80342650159</t>
+  </si>
+  <si>
     <t>CAR4074</t>
   </si>
   <si>
@@ -4028,6 +4040,18 @@
     <t>CHNDLA37T54F205A</t>
   </si>
   <si>
+    <t>MAS7875</t>
+  </si>
+  <si>
+    <t>MASPERO 30</t>
+  </si>
+  <si>
+    <t>Via Maspero Paolo, 30 S.1</t>
+  </si>
+  <si>
+    <t>95617210158</t>
+  </si>
+  <si>
     <t>MOL1254</t>
   </si>
   <si>
@@ -4061,6 +4085,18 @@
     <t>95599760154</t>
   </si>
   <si>
+    <t>CAL5079</t>
+  </si>
+  <si>
+    <t>CALATAFIMI 1/3 BUCCINASCO</t>
+  </si>
+  <si>
+    <t>Via Calatafimi, 13 S.2</t>
+  </si>
+  <si>
+    <t>95671050151</t>
+  </si>
+  <si>
     <t>SIG4442</t>
   </si>
   <si>
@@ -4077,6 +4113,27 @@
   </si>
   <si>
     <t>Via De Togni Aristide, 23</t>
+  </si>
+  <si>
+    <t>NOV3820</t>
+  </si>
+  <si>
+    <t>NOVEGRO 35</t>
+  </si>
+  <si>
+    <t>Via Novegro, 35</t>
+  </si>
+  <si>
+    <t>Segrate</t>
+  </si>
+  <si>
+    <t>NEG4058</t>
+  </si>
+  <si>
+    <t>NEGROLI 9</t>
+  </si>
+  <si>
+    <t>Via Negroli, 9</t>
   </si>
 </sst>
 </file>
@@ -4474,8 +4531,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{40FEE0AB-6D11-C1BE-B96A-19EA3A7E9B16}" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:CV321"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{CF8BB899-55C1-C2AF-530C-72F237C9937C}" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:CV326"/>
   <sheetFormatPr defaultColWidth="8.8515625" customHeight="1" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.28125" customWidth="1"/>
@@ -16162,7 +16219,7 @@
         <v>16</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>18</v>
@@ -16200,7 +16257,7 @@
         <v>16</v>
       </c>
       <c r="F309" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G309" s="3" t="s">
         <v>18</v>
@@ -16218,7 +16275,7 @@
         <v>20</v>
       </c>
       <c r="L309" s="3" t="s">
-        <v>321</v>
+        <v>191</v>
       </c>
     </row>
     <row customHeight="1" ht="15">
@@ -16238,7 +16295,7 @@
         <v>16</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>18</v>
@@ -16256,7 +16313,7 @@
         <v>20</v>
       </c>
       <c r="L310" s="2" t="s">
-        <v>345</v>
+        <v>321</v>
       </c>
     </row>
     <row customHeight="1" ht="15">
@@ -16270,13 +16327,13 @@
         <v>1336</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E311" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F311" s="3" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="G311" s="3" t="s">
         <v>18</v>
@@ -16288,13 +16345,13 @@
         <v>1337</v>
       </c>
       <c r="J311" s="3" t="s">
-        <v>18</v>
+        <v>1337</v>
       </c>
       <c r="K311" s="3" t="s">
         <v>20</v>
       </c>
       <c r="L311" s="3" t="s">
-        <v>633</v>
+        <v>345</v>
       </c>
     </row>
     <row customHeight="1" ht="15">
@@ -16308,107 +16365,107 @@
         <v>1340</v>
       </c>
       <c r="D312" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E312" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F312" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G312" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H312" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I312" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="J312" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K312" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L312" s="2" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A313" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B313" s="3" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C313" s="3" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D313" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E313" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F313" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G313" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H313" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I313" s="3" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J313" s="3" t="s">
+        <v>1345</v>
+      </c>
+      <c r="K313" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L313" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A314" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C314" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D314" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="E312" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F312" s="2" t="s">
+      <c r="E314" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F314" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="G312" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H312" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I312" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J312" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K312" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L312" s="2" t="s">
+      <c r="G314" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H314" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I314" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J314" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K314" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L314" s="2" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row customHeight="1" ht="15">
-      <c r="A313" s="3" t="s">
-        <v>1341</v>
-      </c>
-      <c r="B313" s="3" t="s">
-        <v>1342</v>
-      </c>
-      <c r="C313" s="3" t="s">
-        <v>1343</v>
-      </c>
-      <c r="D313" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E313" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F313" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G313" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H313" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I313" s="3" t="s">
-        <v>1344</v>
-      </c>
-      <c r="J313" s="3" t="s">
-        <v>1344</v>
-      </c>
-      <c r="K313" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L313" s="3" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row customHeight="1" ht="15">
-      <c r="A314" s="2" t="s">
-        <v>1345</v>
-      </c>
-      <c r="B314" s="2" t="s">
-        <v>1346</v>
-      </c>
-      <c r="C314" s="2" t="s">
-        <v>1347</v>
-      </c>
-      <c r="D314" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E314" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F314" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G314" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H314" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I314" s="2" t="s">
-        <v>1348</v>
-      </c>
-      <c r="J314" s="2" t="s">
-        <v>1348</v>
-      </c>
-      <c r="K314" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L314" s="2" t="s">
-        <v>951</v>
       </c>
     </row>
     <row customHeight="1" ht="15">
@@ -16428,63 +16485,253 @@
         <v>16</v>
       </c>
       <c r="F315" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G315" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H315" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I315" s="3" t="s">
+        <v>1352</v>
+      </c>
+      <c r="J315" s="3" t="s">
+        <v>1352</v>
+      </c>
+      <c r="K315" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L315" s="3" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A316" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C316" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E316" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F316" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G316" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H316" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I316" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="J316" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="K316" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L316" s="2" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A317" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B317" s="3" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C317" s="3" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D317" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E317" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F317" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="G317" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H317" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I317" s="3" t="s">
+        <v>1360</v>
+      </c>
+      <c r="J317" s="3" t="s">
+        <v>1360</v>
+      </c>
+      <c r="K317" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L317" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A318" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C318" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D318" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E318" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F318" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="G315" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H315" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I315" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J315" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K315" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L315" s="3" t="s">
+      <c r="G318" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H318" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I318" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J318" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K318" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L318" s="2" t="s">
         <v>856</v>
       </c>
     </row>
     <row customHeight="1" ht="15">
-      <c r="A316" s="2" t="s">
-        <v>1352</v>
-      </c>
-      <c r="B316" s="2" t="s">
-        <v>1353</v>
-      </c>
-      <c r="C316" s="2" t="s">
-        <v>1354</v>
-      </c>
-      <c r="D316" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E316" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F316" s="2" t="s">
+      <c r="A319" s="3" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B319" s="3" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C319" s="3" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D319" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E319" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F319" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G316" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H316" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I316" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J316" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K316" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L316" s="2" t="s">
+      <c r="G319" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H319" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I319" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J319" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K319" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L319" s="3" t="s">
         <v>321</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A320" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C320" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D320" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="E320" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F320" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="G320" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H320" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I320" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J320" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K320" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L320" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row customHeight="1" ht="15">
+      <c r="A321" s="3" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B321" s="3" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C321" s="3" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D321" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E321" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F321" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G321" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H321" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I321" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J321" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K321" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="L321" s="3" t="s">
+        <v>345</v>
       </c>
     </row>
   </sheetData>
